--- a/artfynd/A 8196-2026 artfynd.xlsx
+++ b/artfynd/A 8196-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,225 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131872464</v>
+      </c>
+      <c r="B3" t="n">
+        <v>4774</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gatan, Gatan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>504399</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6612707</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131872537</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gatan, Gatan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>504409</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6612717</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8196-2026 artfynd.xlsx
+++ b/artfynd/A 8196-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>131872537</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,6 +1017,639 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131914243</v>
+      </c>
+      <c r="B5" t="n">
+        <v>104550</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>200 m O Smedsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>504413</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6612714</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131914235</v>
+      </c>
+      <c r="B6" t="n">
+        <v>104550</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>200 m O Smedsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>504442</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6612773</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131914232</v>
+      </c>
+      <c r="B7" t="n">
+        <v>4774</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>200 m O Smedsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>504409</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6612712</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131914253</v>
+      </c>
+      <c r="B8" t="n">
+        <v>104550</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>200 m O Smedsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>504402</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6612707</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131914094</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101249</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>200 m O Smedsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>504436</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6612763</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131914239</v>
+      </c>
+      <c r="B10" t="n">
+        <v>104550</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>200 m O Smedsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>504424</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6612738</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8196-2026 artfynd.xlsx
+++ b/artfynd/A 8196-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>131872464</v>
       </c>
       <c r="B3" t="n">
-        <v>4774</v>
+        <v>4775</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>131872537</v>
       </c>
       <c r="B4" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>131914243</v>
       </c>
       <c r="B5" t="n">
-        <v>104550</v>
+        <v>104554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>131914235</v>
       </c>
       <c r="B6" t="n">
-        <v>104550</v>
+        <v>104554</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>131914232</v>
       </c>
       <c r="B7" t="n">
-        <v>4774</v>
+        <v>4775</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>131914253</v>
       </c>
       <c r="B8" t="n">
-        <v>104550</v>
+        <v>104554</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>131914094</v>
       </c>
       <c r="B9" t="n">
-        <v>101249</v>
+        <v>101252</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>131914239</v>
       </c>
       <c r="B10" t="n">
-        <v>104550</v>
+        <v>104554</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8196-2026 artfynd.xlsx
+++ b/artfynd/A 8196-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>131872537</v>
       </c>
       <c r="B4" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>131914243</v>
       </c>
       <c r="B5" t="n">
-        <v>104554</v>
+        <v>104559</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>131914235</v>
       </c>
       <c r="B6" t="n">
-        <v>104554</v>
+        <v>104559</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>131914253</v>
       </c>
       <c r="B8" t="n">
-        <v>104554</v>
+        <v>104559</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>131914094</v>
       </c>
       <c r="B9" t="n">
-        <v>101252</v>
+        <v>101257</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>131914239</v>
       </c>
       <c r="B10" t="n">
-        <v>104554</v>
+        <v>104559</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,6 +1651,431 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132122904</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101257</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>504433</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6612776</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132122905</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106744</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>504383</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6612692</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132122903</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58069</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>504434</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6612776</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132122906</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91270</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fyrflikig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Geastrum quadrifidum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>504430</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6612770</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8196-2026 artfynd.xlsx
+++ b/artfynd/A 8196-2026 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>131872537</v>
       </c>
       <c r="B4" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>131914243</v>
       </c>
       <c r="B5" t="n">
-        <v>104559</v>
+        <v>104562</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>131914235</v>
       </c>
       <c r="B6" t="n">
-        <v>104559</v>
+        <v>104562</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>131914253</v>
       </c>
       <c r="B8" t="n">
-        <v>104559</v>
+        <v>104562</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>131914094</v>
       </c>
       <c r="B9" t="n">
-        <v>101257</v>
+        <v>101260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>131914239</v>
       </c>
       <c r="B10" t="n">
-        <v>104559</v>
+        <v>104562</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>132122904</v>
       </c>
       <c r="B11" t="n">
-        <v>101257</v>
+        <v>101260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>132122905</v>
       </c>
       <c r="B12" t="n">
-        <v>106744</v>
+        <v>106747</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>132122903</v>
       </c>
       <c r="B13" t="n">
-        <v>58069</v>
+        <v>58071</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>132122906</v>
       </c>
       <c r="B14" t="n">
-        <v>91270</v>
+        <v>91272</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8196-2026 artfynd.xlsx
+++ b/artfynd/A 8196-2026 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>131914243</v>
       </c>
       <c r="B5" t="n">
-        <v>104603</v>
+        <v>104606</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>131914235</v>
       </c>
       <c r="B6" t="n">
-        <v>104603</v>
+        <v>104606</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>131914253</v>
       </c>
       <c r="B8" t="n">
-        <v>104603</v>
+        <v>104606</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>131914094</v>
       </c>
       <c r="B9" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>131914239</v>
       </c>
       <c r="B10" t="n">
-        <v>104603</v>
+        <v>104606</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>132122904</v>
       </c>
       <c r="B11" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>132122905</v>
       </c>
       <c r="B12" t="n">
-        <v>106788</v>
+        <v>106791</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>132122903</v>
       </c>
       <c r="B13" t="n">
-        <v>58105</v>
+        <v>58107</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>132122906</v>
       </c>
       <c r="B14" t="n">
-        <v>91313</v>
+        <v>91316</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8196-2026 artfynd.xlsx
+++ b/artfynd/A 8196-2026 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>131872537</v>
       </c>
       <c r="B4" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>131914243</v>
       </c>
       <c r="B5" t="n">
-        <v>104606</v>
+        <v>104614</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>131914235</v>
       </c>
       <c r="B6" t="n">
-        <v>104606</v>
+        <v>104614</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>131914253</v>
       </c>
       <c r="B8" t="n">
-        <v>104606</v>
+        <v>104614</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>131914094</v>
       </c>
       <c r="B9" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>131914239</v>
       </c>
       <c r="B10" t="n">
-        <v>104606</v>
+        <v>104614</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>132122904</v>
       </c>
       <c r="B11" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>132122905</v>
       </c>
       <c r="B12" t="n">
-        <v>106791</v>
+        <v>106799</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>132122903</v>
       </c>
       <c r="B13" t="n">
-        <v>58107</v>
+        <v>58108</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>132122906</v>
       </c>
       <c r="B14" t="n">
-        <v>91316</v>
+        <v>91322</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8196-2026 artfynd.xlsx
+++ b/artfynd/A 8196-2026 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>131914243</v>
       </c>
       <c r="B5" t="n">
-        <v>104614</v>
+        <v>104625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>131914235</v>
       </c>
       <c r="B6" t="n">
-        <v>104614</v>
+        <v>104625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>131914253</v>
       </c>
       <c r="B8" t="n">
-        <v>104614</v>
+        <v>104625</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>131914094</v>
       </c>
       <c r="B9" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>131914239</v>
       </c>
       <c r="B10" t="n">
-        <v>104614</v>
+        <v>104625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>132122904</v>
       </c>
       <c r="B11" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>132122905</v>
       </c>
       <c r="B12" t="n">
-        <v>106799</v>
+        <v>106810</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>132122903</v>
       </c>
       <c r="B13" t="n">
-        <v>58108</v>
+        <v>58112</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>132122906</v>
       </c>
       <c r="B14" t="n">
-        <v>91322</v>
+        <v>91332</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8196-2026 artfynd.xlsx
+++ b/artfynd/A 8196-2026 artfynd.xlsx
@@ -1656,7 +1656,7 @@
         <v>132122904</v>
       </c>
       <c r="B11" t="n">
-        <v>101323</v>
+        <v>101325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>132122905</v>
       </c>
       <c r="B12" t="n">
-        <v>106810</v>
+        <v>106812</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>132122906</v>
       </c>
       <c r="B14" t="n">
-        <v>91332</v>
+        <v>91333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8196-2026 artfynd.xlsx
+++ b/artfynd/A 8196-2026 artfynd.xlsx
@@ -1656,7 +1656,7 @@
         <v>132122904</v>
       </c>
       <c r="B11" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>132122905</v>
       </c>
       <c r="B12" t="n">
-        <v>106812</v>
+        <v>106813</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 8196-2026 artfynd.xlsx
+++ b/artfynd/A 8196-2026 artfynd.xlsx
@@ -1656,7 +1656,7 @@
         <v>132122904</v>
       </c>
       <c r="B11" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>132122905</v>
       </c>
       <c r="B12" t="n">
-        <v>106813</v>
+        <v>106814</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>132122903</v>
       </c>
       <c r="B13" t="n">
-        <v>58112</v>
+        <v>58113</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>132122906</v>
       </c>
       <c r="B14" t="n">
-        <v>91333</v>
+        <v>91334</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8196-2026 artfynd.xlsx
+++ b/artfynd/A 8196-2026 artfynd.xlsx
@@ -1656,7 +1656,7 @@
         <v>132122904</v>
       </c>
       <c r="B11" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>132122905</v>
       </c>
       <c r="B12" t="n">
-        <v>106814</v>
+        <v>106816</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>132122906</v>
       </c>
       <c r="B14" t="n">
-        <v>91334</v>
+        <v>91336</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8196-2026 artfynd.xlsx
+++ b/artfynd/A 8196-2026 artfynd.xlsx
@@ -1656,7 +1656,7 @@
         <v>132122904</v>
       </c>
       <c r="B11" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>132122905</v>
       </c>
       <c r="B12" t="n">
-        <v>106816</v>
+        <v>106817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>132122906</v>
       </c>
       <c r="B14" t="n">
-        <v>91336</v>
+        <v>91337</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 8196-2026 artfynd.xlsx
+++ b/artfynd/A 8196-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2445,6 +2445,375 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133719549</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58243</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>504443</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6612728</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133719981</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58243</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>504435</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6612735</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133719553</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58332</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>504443</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6612728</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8196-2026 artfynd.xlsx
+++ b/artfynd/A 8196-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2814,6 +2814,257 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134081994</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58444</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>504454</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6612764</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134081798</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58243</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>504441</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6612723</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2sång, 2 lock. Uppenbarligen 2 par som markerade sina revirgränser</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8196-2026 artfynd.xlsx
+++ b/artfynd/A 8196-2026 artfynd.xlsx
@@ -2081,7 +2081,7 @@
         <v>133408137</v>
       </c>
       <c r="B15" t="n">
-        <v>58243</v>
+        <v>58250</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>133408145</v>
       </c>
       <c r="B16" t="n">
-        <v>58444</v>
+        <v>58451</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>133408140</v>
       </c>
       <c r="B17" t="n">
-        <v>58444</v>
+        <v>58451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>133719549</v>
       </c>
       <c r="B18" t="n">
-        <v>58243</v>
+        <v>58250</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>133719981</v>
       </c>
       <c r="B19" t="n">
-        <v>58243</v>
+        <v>58250</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>133719553</v>
       </c>
       <c r="B20" t="n">
-        <v>58332</v>
+        <v>58339</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>134081994</v>
       </c>
       <c r="B21" t="n">
-        <v>58444</v>
+        <v>58451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>134081798</v>
       </c>
       <c r="B22" t="n">
-        <v>58243</v>
+        <v>58250</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 8196-2026 artfynd.xlsx
+++ b/artfynd/A 8196-2026 artfynd.xlsx
@@ -2081,7 +2081,7 @@
         <v>133408137</v>
       </c>
       <c r="B15" t="n">
-        <v>58250</v>
+        <v>58260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>133408145</v>
       </c>
       <c r="B16" t="n">
-        <v>58451</v>
+        <v>58461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>133408140</v>
       </c>
       <c r="B17" t="n">
-        <v>58451</v>
+        <v>58461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>133719549</v>
       </c>
       <c r="B18" t="n">
-        <v>58250</v>
+        <v>58260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>133719981</v>
       </c>
       <c r="B19" t="n">
-        <v>58250</v>
+        <v>58260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>133719553</v>
       </c>
       <c r="B20" t="n">
-        <v>58339</v>
+        <v>58349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>134081994</v>
       </c>
       <c r="B21" t="n">
-        <v>58451</v>
+        <v>58461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>134081798</v>
       </c>
       <c r="B22" t="n">
-        <v>58250</v>
+        <v>58260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 8196-2026 artfynd.xlsx
+++ b/artfynd/A 8196-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98207934</v>
+        <v>132122906</v>
       </c>
       <c r="B2" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91398</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>2008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lejaskogens naturreservat, norr om, Vstm</t>
+          <t>Leja, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504405.7036570602</v>
+        <v>504430</v>
       </c>
       <c r="R2" t="n">
-        <v>6612694.860252394</v>
+        <v>6612770</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,42 +765,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Örtbarrskog, nordvästsluttning</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Block</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131872464</v>
+        <v>98207934</v>
       </c>
       <c r="B3" t="n">
-        <v>4775</v>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,37 +795,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100299</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gatan, Gatan, Vstm</t>
+          <t>Lejaskogens naturreservat, norr om, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504399</v>
+        <v>504405</v>
       </c>
       <c r="R3" t="n">
-        <v>6612707</v>
+        <v>6612695</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +849,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:25</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:25</t>
+          <t>2021-10-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,69 +865,82 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Örtbarrskog, nordvästsluttning</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131872537</v>
+        <v>131914153</v>
       </c>
       <c r="B4" t="n">
-        <v>57946</v>
+        <v>96410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2812</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gatan, Gatan, Vstm</t>
+          <t>200 m O Smedsjön, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504409</v>
+        <v>504439</v>
       </c>
       <c r="R4" t="n">
-        <v>6612717</v>
+        <v>6612767</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,22 +964,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Dominant i bottenskiktet</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,28 +983,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131914243</v>
+        <v>98207930</v>
       </c>
       <c r="B5" t="n">
-        <v>104625</v>
+        <v>91680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,45 +1013,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>200 m O Smedsjön, Vstm</t>
+          <t>Lejaskogens naturreservat, norr om, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504413</v>
+        <v>504402</v>
       </c>
       <c r="R5" t="n">
-        <v>6612714</v>
+        <v>6612668</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2021-10-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,29 +1081,37 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131914235</v>
+        <v>131872537</v>
       </c>
       <c r="B6" t="n">
-        <v>104625</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1137,45 +1119,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>200 m O Smedsjön, Vstm</t>
+          <t>Gatan, Gatan, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504442</v>
+        <v>504409</v>
       </c>
       <c r="R6" t="n">
-        <v>6612773</v>
+        <v>6612717</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,12 +1178,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,29 +1202,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131914232</v>
+        <v>131873400</v>
       </c>
       <c r="B7" t="n">
-        <v>4775</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,46 +1231,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>200 m O Smedsjön, Vstm</t>
+          <t>Gatan, Gatan, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504409</v>
+        <v>504391</v>
       </c>
       <c r="R7" t="n">
-        <v>6612712</v>
+        <v>6612670</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1306,12 +1290,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,29 +1314,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131914253</v>
+        <v>131872464</v>
       </c>
       <c r="B8" t="n">
-        <v>104625</v>
+        <v>4776</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,45 +1343,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>200 m O Smedsjön, Vstm</t>
+          <t>Gatan, Gatan, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504402</v>
+        <v>504399</v>
       </c>
       <c r="R8" t="n">
         <v>6612707</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,12 +1397,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,29 +1421,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131914094</v>
+        <v>131914232</v>
       </c>
       <c r="B9" t="n">
-        <v>101323</v>
+        <v>4776</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,27 +1450,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1484,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504436</v>
+        <v>504409</v>
       </c>
       <c r="R9" t="n">
-        <v>6612763</v>
+        <v>6612712</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,32 +1546,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131914239</v>
+        <v>133408051</v>
       </c>
       <c r="B10" t="n">
-        <v>104625</v>
+        <v>58260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222412</v>
+        <v>103012</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1580,23 +1579,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>200 m O Smedsjön, Vstm</t>
+          <t>Lejaskogen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504424</v>
+        <v>504419</v>
       </c>
       <c r="R10" t="n">
-        <v>6612738</v>
+        <v>6612648</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1620,12 +1623,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>03:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,76 +1647,82 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132122904</v>
+        <v>133408137</v>
       </c>
       <c r="B11" t="n">
-        <v>101330</v>
+        <v>58260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>103012</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Leja, Vstm</t>
+          <t>Lejaskogen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>504433</v>
+        <v>504452</v>
       </c>
       <c r="R11" t="n">
-        <v>6612776</v>
+        <v>6612737</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1727,12 +1746,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>03:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1747,44 +1776,48 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132122905</v>
+        <v>133408254</v>
       </c>
       <c r="B12" t="n">
-        <v>106817</v>
+        <v>58260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220785</v>
+        <v>103012</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1792,19 +1825,27 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Leja, Vstm</t>
+          <t>Lejaskogen, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504383</v>
+        <v>504343</v>
       </c>
       <c r="R12" t="n">
-        <v>6612692</v>
+        <v>6612698</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1828,12 +1869,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>03:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,22 +1899,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132122903</v>
+        <v>133719549</v>
       </c>
       <c r="B13" t="n">
-        <v>58113</v>
+        <v>58260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,49 +1926,49 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103020</v>
+        <v>103012</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Leja, Vstm</t>
+          <t>Lejaskogen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504434</v>
+        <v>504443</v>
       </c>
       <c r="R13" t="n">
-        <v>6612776</v>
+        <v>6612728</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1937,12 +1992,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,22 +2022,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132122906</v>
+        <v>133719981</v>
       </c>
       <c r="B14" t="n">
-        <v>91337</v>
+        <v>58260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,21 +2049,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2008</v>
+        <v>103012</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2002,26 +2071,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Leja, Vstm</t>
+          <t>Lejaskogen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>504430</v>
+        <v>504435</v>
       </c>
       <c r="R14" t="n">
-        <v>6612770</v>
+        <v>6612735</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2045,12 +2115,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2059,26 +2139,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133408137</v>
+        <v>134081798</v>
       </c>
       <c r="B15" t="n">
         <v>58260</v>
@@ -2108,7 +2191,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -2125,10 +2208,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504452</v>
+        <v>504441</v>
       </c>
       <c r="R15" t="n">
-        <v>6612737</v>
+        <v>6612723</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2155,22 +2238,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2sång, 2 lock. Uppenbarligen 2 par som markerade sina revirgränser</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2201,10 +2289,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133408145</v>
+        <v>134381715</v>
       </c>
       <c r="B16" t="n">
-        <v>58461</v>
+        <v>58260</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2212,21 +2300,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103018</v>
+        <v>103012</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2238,7 +2326,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2248,10 +2336,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504479</v>
+        <v>504494</v>
       </c>
       <c r="R16" t="n">
-        <v>6612833</v>
+        <v>6612819</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2278,17 +2366,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2324,60 +2412,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133408140</v>
+        <v>131872897</v>
       </c>
       <c r="B17" t="n">
-        <v>58461</v>
+        <v>58349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lejaskogen, Vstm</t>
+          <t>Gatan, Gatan, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>504452</v>
+        <v>504395</v>
       </c>
       <c r="R17" t="n">
-        <v>6612737</v>
+        <v>6612671</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2401,22 +2482,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,53 +2512,49 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133719549</v>
+        <v>133408026</v>
       </c>
       <c r="B18" t="n">
-        <v>58260</v>
+        <v>58349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2494,10 +2571,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>504443</v>
+        <v>504419</v>
       </c>
       <c r="R18" t="n">
-        <v>6612728</v>
+        <v>6612648</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2524,22 +2601,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2570,32 +2647,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133719981</v>
+        <v>133719553</v>
       </c>
       <c r="B19" t="n">
-        <v>58260</v>
+        <v>58349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2617,10 +2694,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504435</v>
+        <v>504443</v>
       </c>
       <c r="R19" t="n">
-        <v>6612735</v>
+        <v>6612728</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2693,7 +2770,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133719553</v>
+        <v>134381697</v>
       </c>
       <c r="B20" t="n">
         <v>58349</v>
@@ -2740,10 +2817,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>504443</v>
+        <v>504441</v>
       </c>
       <c r="R20" t="n">
-        <v>6612728</v>
+        <v>6612727</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2770,22 +2847,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2816,14 +2893,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134081994</v>
+        <v>133408103</v>
       </c>
       <c r="B21" t="n">
         <v>58461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2863,10 +2940,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>504454</v>
+        <v>504419</v>
       </c>
       <c r="R21" t="n">
-        <v>6612764</v>
+        <v>6612648</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2893,22 +2970,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2939,37 +3016,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134081798</v>
+        <v>133408140</v>
       </c>
       <c r="B22" t="n">
-        <v>58260</v>
+        <v>58461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103012</v>
+        <v>103018</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2986,10 +3063,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>504441</v>
+        <v>504452</v>
       </c>
       <c r="R22" t="n">
-        <v>6612723</v>
+        <v>6612737</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3016,27 +3093,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2sång, 2 lock. Uppenbarligen 2 par som markerade sina revirgränser</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3067,10 +3139,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134381697</v>
+        <v>133408145</v>
       </c>
       <c r="B23" t="n">
-        <v>58349</v>
+        <v>58461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3078,21 +3150,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3104,7 +3176,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3114,10 +3186,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504441</v>
+        <v>504479</v>
       </c>
       <c r="R23" t="n">
-        <v>6612727</v>
+        <v>6612833</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3144,17 +3216,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3183,6 +3255,1331 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>133719543</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>504355</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6612728</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134081994</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>504454</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6612764</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132122903</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58134</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>504434</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6612776</v>
+      </c>
+      <c r="S26" t="n">
+        <v>50</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>133719535</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>504395</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6612662</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132122905</v>
+      </c>
+      <c r="B28" t="n">
+        <v>106894</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>504383</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6612692</v>
+      </c>
+      <c r="S28" t="n">
+        <v>50</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131914235</v>
+      </c>
+      <c r="B29" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>200 m O Smedsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>504442</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6612773</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131914239</v>
+      </c>
+      <c r="B30" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>200 m O Smedsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>504424</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6612738</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131914243</v>
+      </c>
+      <c r="B31" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>200 m O Smedsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>504413</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6612714</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131914253</v>
+      </c>
+      <c r="B32" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>200 m O Smedsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>504402</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6612707</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131914094</v>
+      </c>
+      <c r="B33" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>200 m O Smedsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>504436</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6612763</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132122904</v>
+      </c>
+      <c r="B34" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>504433</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6612776</v>
+      </c>
+      <c r="S34" t="n">
+        <v>50</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>133408259</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101305</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>504343</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6612698</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>

--- a/artfynd/A 8196-2026 artfynd.xlsx
+++ b/artfynd/A 8196-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132122906</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98207934</t>
         </is>
       </c>
     </row>
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914153</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98207930</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131872537</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131873400</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1436,6 +1471,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131872464</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1543,6 +1583,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914232</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1666,6 +1711,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133408051</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1789,6 +1839,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133408137</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1912,6 +1967,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133408254</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2035,6 +2095,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133719549</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2158,6 +2223,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133719981</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2286,6 +2356,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134081798</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2409,6 +2484,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134381715</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2521,6 +2601,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131872897</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2644,6 +2729,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133408026</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2767,6 +2857,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133719553</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2890,6 +2985,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134381697</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3013,6 +3113,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133408103</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3136,6 +3241,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133408140</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3259,6 +3369,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133408145</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3382,6 +3497,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133719543</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3505,6 +3625,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134081994</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3614,6 +3739,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132122903</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3735,6 +3865,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133719535</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3836,6 +3971,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132122905</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3942,6 +4082,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914235</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4048,6 +4193,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914239</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4154,6 +4304,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914243</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4260,6 +4415,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914253</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4362,6 +4522,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131914094</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4468,6 +4633,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132122904</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4584,8 +4754,49 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133408259</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>